--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/9105-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/9105-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F52D3F98-E39A-4260-A742-282EF46D11E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8EC61552-8166-4480-9A45-ABC5771CA757}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{59B3BF01-26A0-4CAC-BDDE-CD587CF68874}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{01B6DE23-E5CC-4E64-A474-B0C30976922D}"/>
   </bookViews>
   <sheets>
     <sheet name="9105-dividend-20260225_0_4" sheetId="1" r:id="rId1"/>
@@ -1514,23 +1514,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{388A7B08-786D-44B6-BC37-B61C337E6D3B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C1784EB-4B16-43F9-B34B-0DA107B2DD30}">
   <dimension ref="A1:R45"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="7.33203125" customWidth="1"/>
-    <col min="3" max="3" width="8" customWidth="1"/>
-    <col min="4" max="4" width="8.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="6" max="7" width="8.33203125" customWidth="1"/>
-    <col min="8" max="8" width="8" customWidth="1"/>
-    <col min="9" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="9" customWidth="1"/>
+    <col min="1" max="1" width="6.5" customWidth="1"/>
+    <col min="2" max="2" width="9.25" customWidth="1"/>
+    <col min="3" max="3" width="10" customWidth="1"/>
+    <col min="4" max="4" width="10.5" customWidth="1"/>
+    <col min="5" max="5" width="10" customWidth="1"/>
+    <col min="6" max="7" width="10.5" customWidth="1"/>
+    <col min="8" max="8" width="10" customWidth="1"/>
+    <col min="9" max="10" width="10.5" customWidth="1"/>
+    <col min="11" max="17" width="10" customWidth="1"/>
+    <col min="18" max="18" width="10.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1558,7 +1558,7 @@
       <c r="Q1" s="30"/>
       <c r="R1" s="22"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
@@ -1588,7 +1588,7 @@
       <c r="Q2" s="32"/>
       <c r="R2" s="33"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
@@ -1634,7 +1634,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="25"/>
       <c r="B4" s="26"/>
       <c r="C4" s="7"/>
@@ -1684,7 +1684,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="37">
         <v>2025</v>
       </c>
@@ -1738,7 +1738,7 @@
         <v>2.63</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>25</v>
       </c>
@@ -1794,7 +1794,7 @@
         <v>1.06</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>25</v>
       </c>
@@ -1850,7 +1850,7 @@
         <v>1.58</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="39">
         <v>2024</v>
       </c>
@@ -1904,7 +1904,7 @@
         <v>2.85</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
         <v>25</v>
       </c>
@@ -1960,7 +1960,7 @@
         <v>1.04</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="17" t="s">
         <v>25</v>
       </c>
@@ -2016,7 +2016,7 @@
         <v>1.81</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="37">
         <v>2023</v>
       </c>
@@ -2070,7 +2070,7 @@
         <v>21.9</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
         <v>25</v>
       </c>
@@ -2126,7 +2126,7 @@
         <v>0.93</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>25</v>
       </c>
@@ -2182,7 +2182,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="39">
         <v>2022</v>
       </c>
@@ -2236,7 +2236,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="17" t="s">
         <v>25</v>
       </c>
@@ -2292,7 +2292,7 @@
         <v>0.43</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="17" t="s">
         <v>25</v>
       </c>
@@ -2348,7 +2348,7 @@
         <v>18.100000000000001</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="37">
         <v>2021</v>
       </c>
@@ -2402,7 +2402,7 @@
         <v>20.399999999999999</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
         <v>25</v>
       </c>
@@ -2458,7 +2458,7 @@
         <v>0.39</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
         <v>25</v>
       </c>
@@ -2514,7 +2514,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="39">
         <v>2020</v>
       </c>
@@ -2568,7 +2568,7 @@
         <v>1.74</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="17" t="s">
         <v>25</v>
       </c>
@@ -2624,7 +2624,7 @@
         <v>0.42</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="17" t="s">
         <v>25</v>
       </c>
@@ -2680,7 +2680,7 @@
         <v>1.32</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="37">
         <v>2019</v>
       </c>
@@ -2734,7 +2734,7 @@
         <v>3.71</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
         <v>25</v>
       </c>
@@ -2790,7 +2790,7 @@
         <v>2.56</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
         <v>25</v>
       </c>
@@ -2846,7 +2846,7 @@
         <v>1.1599999999999999</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="39">
         <v>2018</v>
       </c>
@@ -2900,7 +2900,7 @@
         <v>3.4</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="17" t="s">
         <v>25</v>
       </c>
@@ -2956,7 +2956,7 @@
         <v>2.06</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="17" t="s">
         <v>25</v>
       </c>
@@ -3012,7 +3012,7 @@
         <v>1.35</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="37">
         <v>2017</v>
       </c>
@@ -3066,7 +3066,7 @@
         <v>2.91</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="11" t="s">
         <v>25</v>
       </c>
@@ -3122,7 +3122,7 @@
         <v>1.78</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="11" t="s">
         <v>25</v>
       </c>
@@ -3178,7 +3178,7 @@
         <v>1.1299999999999999</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="39">
         <v>2016</v>
       </c>
@@ -3232,7 +3232,7 @@
         <v>3.6</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="37">
         <v>2015</v>
       </c>
@@ -3286,7 +3286,7 @@
         <v>2.65</v>
       </c>
     </row>
-    <row r="34" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="39">
         <v>2014</v>
       </c>
@@ -3340,7 +3340,7 @@
         <v>3.76</v>
       </c>
     </row>
-    <row r="35" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="37">
         <v>2013</v>
       </c>
@@ -3394,7 +3394,7 @@
         <v>4.1100000000000003</v>
       </c>
     </row>
-    <row r="36" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="39">
         <v>2012</v>
       </c>
@@ -3448,7 +3448,7 @@
         <v>3.93</v>
       </c>
     </row>
-    <row r="37" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="37">
         <v>2011</v>
       </c>
@@ -3502,7 +3502,7 @@
         <v>3.04</v>
       </c>
     </row>
-    <row r="38" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="39">
         <v>2010</v>
       </c>
@@ -3556,7 +3556,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="39" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="37">
         <v>2009</v>
       </c>
@@ -3610,7 +3610,7 @@
         <v>3.44</v>
       </c>
     </row>
-    <row r="40" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="39">
         <v>2008</v>
       </c>
@@ -3664,7 +3664,7 @@
         <v>4.95</v>
       </c>
     </row>
-    <row r="41" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A41" s="37">
         <v>2007</v>
       </c>
@@ -3718,7 +3718,7 @@
         <v>5.13</v>
       </c>
     </row>
-    <row r="42" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A42" s="39">
         <v>2006</v>
       </c>
@@ -3772,7 +3772,7 @@
         <v>4.03</v>
       </c>
     </row>
-    <row r="43" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A43" s="37">
         <v>2005</v>
       </c>
@@ -3826,7 +3826,7 @@
         <v>5.87</v>
       </c>
     </row>
-    <row r="44" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A44" s="39">
         <v>2004</v>
       </c>
@@ -3880,7 +3880,7 @@
         <v>3.34</v>
       </c>
     </row>
-    <row r="45" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A45" s="37" t="s">
         <v>57</v>
       </c>
